--- a/data/trans_orig/IP25A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP25A_R-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>17675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14661</t>
+          <t>14932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26534</t>
+          <t>26566</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>25014</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40920</t>
+          <t>40185</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>40,78%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28270</t>
+          <t>27544</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37548</t>
+          <t>36994</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26790</t>
+          <t>26758</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38663</t>
+          <t>38392</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57623</t>
+          <t>58358</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73719</t>
+          <t>73529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,62%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27269</t>
+          <t>27691</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41950</t>
+          <t>42925</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30509</t>
+          <t>30632</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45614</t>
+          <t>46654</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62616</t>
+          <t>62158</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83813</t>
+          <t>84152</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,62%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46867</t>
+          <t>45892</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61548</t>
+          <t>61126</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50051</t>
+          <t>49011</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65156</t>
+          <t>65033</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100669</t>
+          <t>100330</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>121866</t>
+          <t>122324</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,31%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23116</t>
+          <t>23620</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36699</t>
+          <t>36555</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33326</t>
+          <t>32172</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47120</t>
+          <t>47785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66107</t>
+          <t>65838</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,48%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25274</t>
+          <t>25418</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38857</t>
+          <t>38353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32602</t>
+          <t>33756</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45530</t>
+          <t>46141</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61794</t>
+          <t>62063</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80781</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,64%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>13922</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25315</t>
+          <t>25704</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20203</t>
+          <t>19956</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33604</t>
+          <t>32908</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36745</t>
+          <t>37365</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54905</t>
+          <t>54834</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44719</t>
+          <t>44330</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56509</t>
+          <t>56112</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39074</t>
+          <t>39770</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52475</t>
+          <t>52722</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87807</t>
+          <t>87878</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>105967</t>
+          <t>105347</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,82%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15788</t>
+          <t>15606</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19076</t>
+          <t>18956</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>18360</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31233</t>
+          <t>31003</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,93%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18193</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27327</t>
+          <t>27451</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15948</t>
+          <t>16068</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25306</t>
+          <t>25781</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37772</t>
+          <t>38002</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50138</t>
+          <t>50645</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19715</t>
+          <t>18894</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31205</t>
+          <t>30538</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19016</t>
+          <t>18528</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30523</t>
+          <t>30202</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41991</t>
+          <t>42562</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57976</t>
+          <t>58265</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,89%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20883</t>
+          <t>21550</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32373</t>
+          <t>33194</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23537</t>
+          <t>23858</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35044</t>
+          <t>35532</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48172</t>
+          <t>47883</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>64157</t>
+          <t>63586</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>59,9%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45728</t>
+          <t>44571</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63150</t>
+          <t>63074</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60078</t>
+          <t>61242</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93675</t>
+          <t>93496</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>117858</t>
+          <t>119450</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>50,12%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>55920</t>
+          <t>55996</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>73342</t>
+          <t>74499</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59198</t>
+          <t>58034</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>120488</t>
+          <t>118896</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>144671</t>
+          <t>144850</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,77%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29059</t>
+          <t>29671</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45253</t>
+          <t>47010</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30641</t>
+          <t>31272</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47587</t>
+          <t>49113</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>64544</t>
+          <t>65555</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>89279</t>
+          <t>90449</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>97316</t>
+          <t>95559</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>113510</t>
+          <t>112898</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>88406</t>
+          <t>86880</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>105352</t>
+          <t>104721</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>189283</t>
+          <t>188113</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>214018</t>
+          <t>213007</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,47%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>204283</t>
+          <t>203162</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>241902</t>
+          <t>242286</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>221272</t>
+          <t>220854</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>262514</t>
+          <t>261072</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>436116</t>
+          <t>438107</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>490173</t>
+          <t>491761</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>371848</t>
+          <t>371464</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>409467</t>
+          <t>410588</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>369435</t>
+          <t>370877</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>410677</t>
+          <t>411095</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>755526</t>
+          <t>753938</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>809583</t>
+          <t>807592</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,83%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16234</t>
+          <t>15611</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>27428</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20966</t>
+          <t>21038</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33958</t>
+          <t>33712</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40254</t>
+          <t>39827</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57799</t>
+          <t>57741</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,29%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26025</t>
+          <t>26097</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37291</t>
+          <t>37914</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25092</t>
+          <t>25338</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38084</t>
+          <t>38012</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54776</t>
+          <t>54834</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72321</t>
+          <t>72748</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,62%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22365</t>
+          <t>22614</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37270</t>
+          <t>36803</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29154</t>
+          <t>28857</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44709</t>
+          <t>45059</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55727</t>
+          <t>56175</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76212</t>
+          <t>76943</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51736</t>
+          <t>52203</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66641</t>
+          <t>66392</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>53504</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69409</t>
+          <t>69706</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111357</t>
+          <t>110626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>131842</t>
+          <t>131394</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,05%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15810</t>
+          <t>14342</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>14673</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25959</t>
+          <t>26447</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22198</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38525</t>
+          <t>37518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46831</t>
+          <t>48299</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57301</t>
+          <t>57930</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41199</t>
+          <t>40711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53138</t>
+          <t>52485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>91274</t>
+          <t>92281</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>107601</t>
+          <t>107895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23436</t>
+          <t>23131</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36706</t>
+          <t>36621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17513</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30995</t>
+          <t>31364</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43427</t>
+          <t>44379</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63233</t>
+          <t>63778</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32987</t>
+          <t>33072</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46257</t>
+          <t>46562</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43234</t>
+          <t>42865</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56716</t>
+          <t>56653</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80690</t>
+          <t>80145</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>100496</t>
+          <t>99544</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,16%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16547</t>
+          <t>17373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15888</t>
+          <t>15940</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27060</t>
+          <t>27519</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25851</t>
+          <t>25625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40907</t>
+          <t>40657</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,05%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25290</t>
+          <t>24464</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35017</t>
+          <t>34468</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17513</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28685</t>
+          <t>28633</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45503</t>
+          <t>45753</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60559</t>
+          <t>60785</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,34%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>7678</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18494</t>
+          <t>18256</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19583</t>
+          <t>19925</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18241</t>
+          <t>18896</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34234</t>
+          <t>34020</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32421</t>
+          <t>32659</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42989</t>
+          <t>43237</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35892</t>
+          <t>35550</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47206</t>
+          <t>46534</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72156</t>
+          <t>72370</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88149</t>
+          <t>87494</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>26060</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42930</t>
+          <t>42557</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25576</t>
+          <t>25727</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42119</t>
+          <t>43065</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57120</t>
+          <t>56307</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80009</t>
+          <t>79295</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>74534</t>
+          <t>74907</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>91109</t>
+          <t>91404</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>87126</t>
+          <t>86180</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>103669</t>
+          <t>103518</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>166700</t>
+          <t>167414</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>189589</t>
+          <t>190402</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,18%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67589</t>
+          <t>68235</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>87219</t>
+          <t>87185</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60462</t>
+          <t>60741</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>80565</t>
+          <t>81404</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>134342</t>
+          <t>133314</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>161892</t>
+          <t>161839</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59703</t>
+          <t>59737</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>79333</t>
+          <t>78687</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74183</t>
+          <t>73344</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94286</t>
+          <t>94007</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>139778</t>
+          <t>139831</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>167328</t>
+          <t>168356</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,81%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>205233</t>
+          <t>204560</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>246614</t>
+          <t>244649</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>228621</t>
+          <t>228526</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>267905</t>
+          <t>269667</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>445925</t>
+          <t>443391</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>503374</t>
+          <t>498740</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,93%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>385389</t>
+          <t>387354</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>426770</t>
+          <t>427443</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>415137</t>
+          <t>413375</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>454421</t>
+          <t>454516</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>811671</t>
+          <t>816305</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>869120</t>
+          <t>871654</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,28%</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9722</t>
+          <t>10044</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19900</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17974</t>
+          <t>17915</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30617</t>
+          <t>30735</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>31226</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47564</t>
+          <t>47764</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28119</t>
+          <t>27895</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38297</t>
+          <t>37975</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26479</t>
+          <t>26361</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39122</t>
+          <t>39181</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57551</t>
+          <t>57351</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74249</t>
+          <t>73889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,29%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38592</t>
+          <t>38268</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54256</t>
+          <t>54274</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40453</t>
+          <t>41326</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58458</t>
+          <t>57576</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82951</t>
+          <t>83887</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105839</t>
+          <t>107038</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>53,05%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41800</t>
+          <t>41782</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57464</t>
+          <t>57788</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47258</t>
+          <t>48140</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65263</t>
+          <t>64390</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95933</t>
+          <t>94734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>118821</t>
+          <t>117885</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,43%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>16694</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29167</t>
+          <t>29347</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>19641</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32488</t>
+          <t>31759</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>39372</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58076</t>
+          <t>56848</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>49,44%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26998</t>
+          <t>26818</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39676</t>
+          <t>39471</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26336</t>
+          <t>27065</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39543</t>
+          <t>39183</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56913</t>
+          <t>58141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76002</t>
+          <t>75617</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,76%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17963</t>
+          <t>17541</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31259</t>
+          <t>30950</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19036</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33719</t>
+          <t>33678</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41348</t>
+          <t>41030</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60130</t>
+          <t>60310</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36569</t>
+          <t>36878</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49865</t>
+          <t>50287</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42619</t>
+          <t>42660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57302</t>
+          <t>56703</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>84035</t>
+          <t>83855</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102817</t>
+          <t>103135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17186</t>
+          <t>16892</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27449</t>
+          <t>27045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14900</t>
+          <t>14798</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25525</t>
+          <t>25067</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34538</t>
+          <t>35061</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49300</t>
+          <t>49441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,84%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11214</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21477</t>
+          <t>21771</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14950</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25117</t>
+          <t>25219</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29380</t>
+          <t>29239</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44142</t>
+          <t>43619</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,44%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17057</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28307</t>
+          <t>28136</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22615</t>
+          <t>22732</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35685</t>
+          <t>35854</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43042</t>
+          <t>43353</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59632</t>
+          <t>59969</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,23%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>20587</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>31882</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18570</t>
+          <t>18401</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31640</t>
+          <t>31523</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43346</t>
+          <t>43009</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59936</t>
+          <t>59625</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>57,9%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50332</t>
+          <t>50775</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68322</t>
+          <t>69134</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49281</t>
+          <t>51123</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68946</t>
+          <t>69561</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>107825</t>
+          <t>107372</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133351</t>
+          <t>132817</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,14%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>57806</t>
+          <t>56994</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>75796</t>
+          <t>75353</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59662</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>79327</t>
+          <t>77485</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>121385</t>
+          <t>121919</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>146911</t>
+          <t>147364</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,85%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57047</t>
+          <t>56112</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>75788</t>
+          <t>75357</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62358</t>
+          <t>63110</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83246</t>
+          <t>82749</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>125981</t>
+          <t>126146</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>152271</t>
+          <t>153702</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>65003</t>
+          <t>65434</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>83744</t>
+          <t>84679</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70957</t>
+          <t>71454</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91845</t>
+          <t>91093</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>142722</t>
+          <t>141291</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>169012</t>
+          <t>168847</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,24%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>259939</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>300004</t>
+          <t>298730</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>285822</t>
+          <t>284906</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>328199</t>
+          <t>329572</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>556494</t>
+          <t>559183</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>617007</t>
+          <t>616350</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,51%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>322368</t>
+          <t>323642</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>363717</t>
+          <t>362433</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>346857</t>
+          <t>345484</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>389234</t>
+          <t>390150</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>680421</t>
+          <t>681078</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>740934</t>
+          <t>738245</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,9%</t>
         </is>
       </c>
     </row>
